--- a/resul/R1.1.xlsx
+++ b/resul/R1.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/matf8_umsystem_edu/Documents/Desktop/Github/resul/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailmissouri-my.sharepoint.com/personal/matf8_umsystem_edu/Documents/Desktop/github GPV/LLM_GPV/resul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{35327A39-5136-4906-A26A-02233CBD8D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C4F1F3D-1FAD-4B98-B501-A20EE60E41D9}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{35327A39-5136-4906-A26A-02233CBD8D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF59A77-A907-4334-823D-55CA0454CE2D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B8F18BCE-D502-4F01-B661-095CDBA34959}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B8F18BCE-D502-4F01-B661-095CDBA34959}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -215,19 +215,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -243,10 +244,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,14 +564,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A33058-A256-4591-BAFE-D58F770568A0}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -612,8 +610,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="1">
@@ -648,8 +646,8 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="1">
@@ -686,8 +684,8 @@
         <v>7.0800000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1">
@@ -724,8 +722,8 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1">
@@ -760,8 +758,8 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="1">
@@ -798,8 +796,8 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1">
@@ -836,8 +834,8 @@
         <v>5.9400000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1">
@@ -874,8 +872,8 @@
         <v>0.1187</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="1">
@@ -912,8 +910,8 @@
         <v>8.9599999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="1">
@@ -950,8 +948,8 @@
         <v>6.3200000000000006E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="1">
@@ -988,8 +986,8 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="1">
@@ -1026,8 +1024,8 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="1">
@@ -1064,8 +1062,8 @@
         <v>0.1187</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="1">
@@ -1102,8 +1100,8 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1">
@@ -1140,8 +1138,8 @@
         <v>7.7600000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="1">
@@ -1178,8 +1176,8 @@
         <v>8.0619999999999997E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="1">
@@ -1216,8 +1214,8 @@
         <v>0.1119</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="1">
@@ -1254,8 +1252,8 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="1">
@@ -1292,8 +1290,8 @@
         <v>5.5599999999999997E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="1">
@@ -1330,8 +1328,8 @@
         <v>0.1077</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="1">
@@ -1368,8 +1366,8 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="1">
@@ -1406,8 +1404,8 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="1">
@@ -1444,8 +1442,8 @@
         <v>6.9900000000000004E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B24" s="1">
@@ -1482,8 +1480,8 @@
         <v>6.3200000000000006E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B25" s="1">
@@ -1520,8 +1518,8 @@
         <v>5.1200000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B26" s="1">
@@ -1558,8 +1556,8 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B27" s="1">
@@ -1596,8 +1594,8 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
         <v>36</v>
       </c>
       <c r="B28" s="1">
@@ -1634,8 +1632,8 @@
         <v>0.1074</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="1">
@@ -1672,8 +1670,8 @@
         <v>8.2900000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
       <c r="B30" s="1">
@@ -1710,8 +1708,8 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="1">
@@ -1748,8 +1746,8 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="1">
